--- a/data/P2/P2T3_BQ6.xlsx
+++ b/data/P2/P2T3_BQ6.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F94022D-FC0E-F04B-B794-34E1FBB7E994}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8CFB0B1-2B23-5048-80CD-285140763B81}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32920" yWindow="8800" windowWidth="38400" windowHeight="21140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -26,16 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
-  <si>
-    <t>word</t>
-  </si>
-  <si>
-    <t>meaning</t>
-  </si>
-  <si>
-    <t>day</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="140">
   <si>
     <t>sentence</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -284,13 +275,443 @@
   <si>
     <t>關於音樂的感受，沒有對錯之分。</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>phonetics</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>syllable</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>word</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>meaning</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>day</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>單詞 / 短語</t>
+  </si>
+  <si>
+    <t>國際音標</t>
+  </si>
+  <si>
+    <t>音節拆分</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>mu-si-cian</t>
+  </si>
+  <si>
+    <t>mu-si-cal in-stru-ments</t>
+  </si>
+  <si>
+    <t>trum-pet</t>
+  </si>
+  <si>
+    <t>cym-bal</t>
+  </si>
+  <si>
+    <t>/drʌm/</t>
+  </si>
+  <si>
+    <t>vi-o-lin</t>
+  </si>
+  <si>
+    <r>
+      <t>/ha</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ɪ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/ /lə</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ʊ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>/nə</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ʊ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ts/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>/mjuˈz</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ɪʃ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>n/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>/ˈmju</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ː</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>z</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ɪ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>kl ˈ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ɪ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>nstrəmənts/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>/ˈtrʌmp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ɪ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>t/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>/flu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ː</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>t/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>/ˈs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ɪ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>mbl/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>/ˌva</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ɪ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>əˈl</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ɪ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>n/</t>
+    </r>
+  </si>
+  <si>
+    <t>/ɡɪˈtɑː(r)/</t>
+  </si>
+  <si>
+    <t>gui-tar</t>
+  </si>
+  <si>
+    <t>/ˌjuːkəˈleɪli/</t>
+  </si>
+  <si>
+    <t>u-ku-le-le</t>
+  </si>
+  <si>
+    <t>/ˈmelədi/</t>
+  </si>
+  <si>
+    <t>mel-o-dy</t>
+  </si>
+  <si>
+    <t>/laʊd/</t>
+  </si>
+  <si>
+    <t>/sɒft/</t>
+  </si>
+  <si>
+    <t>/ˈdʒentl/</t>
+  </si>
+  <si>
+    <t>gen-tle</t>
+  </si>
+  <si>
+    <t>/ˈstedi/</t>
+  </si>
+  <si>
+    <t>stead-y</t>
+  </si>
+  <si>
+    <t>/kɑːm/</t>
+  </si>
+  <si>
+    <t>/ˈdʒɔɪfl/</t>
+  </si>
+  <si>
+    <t>joy-ful</t>
+  </si>
+  <si>
+    <t>/ˈlaɪvli/</t>
+  </si>
+  <si>
+    <t>live-ly</t>
+  </si>
+  <si>
+    <t>/ɪkˈsaɪtɪd/</t>
+  </si>
+  <si>
+    <t>ex-ci-ted</t>
+  </si>
+  <si>
+    <t>/rɪˈlækst/</t>
+  </si>
+  <si>
+    <t>re-laxed</t>
+  </si>
+  <si>
+    <t>/əˈnɔɪd/</t>
+  </si>
+  <si>
+    <t>an-noyed</t>
+  </si>
+  <si>
+    <t>/bɔːd/</t>
+  </si>
+  <si>
+    <t>/ˈfraɪtnd/</t>
+  </si>
+  <si>
+    <t>fright-ened</t>
+  </si>
+  <si>
+    <t>/ˈæŋkʃəs/</t>
+  </si>
+  <si>
+    <t>an-xious</t>
+  </si>
+  <si>
+    <t>/ɡɪv ə ˈkɒnsət/</t>
+  </si>
+  <si>
+    <t>give a con-cert</t>
+  </si>
+  <si>
+    <t>/ˈsəʊləʊ/</t>
+  </si>
+  <si>
+    <t>so-lo</t>
+  </si>
+  <si>
+    <t>/saɪn ən ˈɔːtəɡrɑːf/</t>
+  </si>
+  <si>
+    <t>sign an au-to-graph</t>
+  </si>
+  <si>
+    <t>/tɔːk tə fænz/</t>
+  </si>
+  <si>
+    <t>/duː ən ˈɪntəvjuː/</t>
+  </si>
+  <si>
+    <t>do an in-ter-view</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -338,6 +759,26 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="PMingLiU"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -347,7 +788,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -370,18 +811,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -393,6 +840,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -675,357 +1128,586 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.83203125" customWidth="1"/>
     <col min="2" max="2" width="33.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.83203125" customWidth="1"/>
+    <col min="4" max="4" width="39.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28" thickBot="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:10" ht="28" thickBot="1">
+      <c r="A1" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1" s="3"/>
+      <c r="H1" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="28" thickBot="1">
+      <c r="A2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D2" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="28" thickBot="1">
+      <c r="A3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="28" thickBot="1">
+      <c r="A4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="H4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="28" thickBot="1">
+      <c r="A5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="28" thickBot="1">
+      <c r="A6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="28" thickBot="1">
+      <c r="A7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-    </row>
-    <row r="2" spans="1:8" ht="28" thickBot="1">
-      <c r="A2" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="D7" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="28" thickBot="1">
+      <c r="A8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="28" thickBot="1">
+      <c r="A9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="28" thickBot="1">
+      <c r="A10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="28" thickBot="1">
+      <c r="A11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="H11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="28" thickBot="1">
+      <c r="A12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="1">
+        <v>3</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="H12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="28" thickBot="1">
+      <c r="A13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="1">
+        <v>3</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="28" thickBot="1">
+      <c r="A14" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="1">
+        <v>3</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="28" thickBot="1">
+      <c r="A15" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="1">
+        <v>3</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="28" thickBot="1">
+      <c r="A16" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="1">
+        <v>3</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="28" thickBot="1">
+      <c r="A17" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="1">
+        <v>4</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="28" thickBot="1">
+      <c r="A18" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="1">
+        <v>4</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="28" thickBot="1">
+      <c r="A19" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="1">
+        <v>4</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="28" thickBot="1">
+      <c r="A20" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="1">
+        <v>4</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="28" thickBot="1">
+      <c r="A21" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C21" s="1">
+        <v>4</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="28" thickBot="1">
+      <c r="A22" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="1">
         <v>5</v>
       </c>
-      <c r="C2" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="28" thickBot="1">
-      <c r="A3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="D22" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="28" thickBot="1">
+      <c r="A23" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="1">
+        <v>5</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="28" thickBot="1">
+      <c r="A24" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="1">
+        <v>5</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="28" thickBot="1">
+      <c r="A25" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="1">
+        <v>5</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="28" thickBot="1">
+      <c r="A26" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="1">
+        <v>5</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="28" thickBot="1">
+      <c r="A27" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="1">
         <v>6</v>
       </c>
-      <c r="C3" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="28" thickBot="1">
-      <c r="A4" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="28" thickBot="1">
-      <c r="A5" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="28" thickBot="1">
-      <c r="A6" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="28" thickBot="1">
-      <c r="A7" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="28" thickBot="1">
-      <c r="A8" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="28" thickBot="1">
-      <c r="A9" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="28" thickBot="1">
-      <c r="A10" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="28" thickBot="1">
-      <c r="A11" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="28" thickBot="1">
-      <c r="A12" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="28" thickBot="1">
-      <c r="A13" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="28" thickBot="1">
-      <c r="A14" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="28" thickBot="1">
-      <c r="A15" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="28" thickBot="1">
-      <c r="A16" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="28" thickBot="1">
-      <c r="A17" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="28" thickBot="1">
-      <c r="A18" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="28" thickBot="1">
-      <c r="A19" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="28" thickBot="1">
-      <c r="A20" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="28" thickBot="1">
-      <c r="A21" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="28" thickBot="1">
-      <c r="A22" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="28" thickBot="1">
-      <c r="A23" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="28" thickBot="1">
-      <c r="A24" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="28" thickBot="1">
-      <c r="A25" s="5" t="s">
+      <c r="D27" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="28" thickBot="1">
+      <c r="A28" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B28" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="28" thickBot="1">
-      <c r="A26" s="5" t="s">
+      <c r="C28" s="1">
+        <v>6</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="28" thickBot="1">
+      <c r="A29" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B29" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="28" thickBot="1">
-      <c r="A27" s="5" t="s">
+      <c r="C29" s="1">
+        <v>6</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="28" thickBot="1">
+      <c r="A30" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B30" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C30" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" ht="28" thickBot="1">
-      <c r="A28" s="5" t="s">
+      <c r="D30" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="28" thickBot="1">
+      <c r="A31" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B31" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="2">
+      <c r="C31" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" ht="28" thickBot="1">
-      <c r="A29" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C29" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="28" thickBot="1">
-      <c r="A30" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30" s="2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="28" thickBot="1">
-      <c r="A31" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C31" s="2">
-        <v>6</v>
+      <c r="D31" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -1044,88 +1726,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>4</v>
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="3:4">
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/data/P2/P2T3_BQ6.xlsx
+++ b/data/P2/P2T3_BQ6.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/homes/ximonlam/Mac/單詞複習網素材/English/data/P2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8CFB0B1-2B23-5048-80CD-285140763B81}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3315860F-3591-8041-A33B-043930C39D97}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32920" yWindow="8800" windowWidth="38400" windowHeight="21140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31260" yWindow="3580" windowWidth="38400" windowHeight="21140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="168">
   <si>
     <t>sentence</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -295,15 +295,6 @@
   <si>
     <t>day</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>單詞 / 短語</t>
-  </si>
-  <si>
-    <t>國際音標</t>
-  </si>
-  <si>
-    <t>音節拆分</t>
   </si>
   <si>
     <t>--</t>
@@ -705,13 +696,107 @@
   </si>
   <si>
     <t>do an in-ter-view</t>
+  </si>
+  <si>
+    <t>English explanation</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>High means a sharp sound; low means a deep sound</t>
+  </si>
+  <si>
+    <t>Short music sounds we sing or play</t>
+  </si>
+  <si>
+    <t>A person who plays music or sings songs</t>
+  </si>
+  <si>
+    <t>Tools we use to make music</t>
+  </si>
+  <si>
+    <t>A metal wind instrument; blow it to make bright sound</t>
+  </si>
+  <si>
+    <t>A long thin wind instrument; blow air to play tunes</t>
+  </si>
+  <si>
+    <t>Round metal plate; hit it for loud clear music</t>
+  </si>
+  <si>
+    <t>Round instrument, hit it with sticks to make beats</t>
+  </si>
+  <si>
+    <t>Small string instrument, play it with a thin bow</t>
+  </si>
+  <si>
+    <t>String instrument; pull strings with your fingers</t>
+  </si>
+  <si>
+    <t>A small guitar with soft light sound</t>
+  </si>
+  <si>
+    <t>A nice line of music notes that we can hum</t>
+  </si>
+  <si>
+    <t>Big, strong sound that you can hear far away</t>
+  </si>
+  <si>
+    <t>Quiet, gentle sound that is not noisy</t>
+  </si>
+  <si>
+    <t>Slow and smooth sound without big noise</t>
+  </si>
+  <si>
+    <t>Music with even, same-speed beats</t>
+  </si>
+  <si>
+    <t>Slow peaceful music that makes you quiet</t>
+  </si>
+  <si>
+    <t>Happy music full of fun</t>
+  </si>
+  <si>
+    <t>Fast and energetic music that makes you want to move</t>
+  </si>
+  <si>
+    <t>Feeling very happy and eager while listening to music</t>
+  </si>
+  <si>
+    <t>Feeling peaceful and not worried</t>
+  </si>
+  <si>
+    <t>Feeling upset about noisy bad music</t>
+  </si>
+  <si>
+    <t>Feeling tired and not interested in the music</t>
+  </si>
+  <si>
+    <t>Scared of loud or strange music sounds</t>
+  </si>
+  <si>
+    <t>Nervous and worried before playing music</t>
+  </si>
+  <si>
+    <t>Play music for many people to watch</t>
+  </si>
+  <si>
+    <t>Music played by only one musician alone</t>
+  </si>
+  <si>
+    <t>Write your name on paper for fans</t>
+  </si>
+  <si>
+    <t>Chat with people who love your music</t>
+  </si>
+  <si>
+    <t>Answer questions from reporters about music</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -736,15 +821,6 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="新細明體"/>
-      <family val="1"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
       <color theme="1"/>
       <name val="新細明體"/>
       <family val="1"/>
@@ -839,14 +915,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1136,578 +1212,633 @@
     <col min="3" max="3" width="9.83203125" customWidth="1"/>
     <col min="4" max="4" width="39.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="35.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.6640625" customWidth="1"/>
     <col min="7" max="7" width="29.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="28" thickBot="1">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:10" ht="25" thickBot="1">
+      <c r="A1" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="G1" s="3"/>
-      <c r="H1" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>87</v>
-      </c>
+      <c r="F1" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
     </row>
     <row r="2" spans="1:10" ht="28" thickBot="1">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="H2" t="s">
-        <v>51</v>
+      <c r="D2" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F2" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="28" thickBot="1">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="1">
         <v>1</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="H3" t="s">
-        <v>52</v>
+      <c r="D3" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F3" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="28" thickBot="1">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="H4" t="s">
-        <v>53</v>
+      <c r="D4" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="28" thickBot="1">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H5" t="s">
-        <v>54</v>
+      <c r="D5" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F5" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="28" thickBot="1">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H6" t="s">
-        <v>55</v>
+      <c r="D6" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F6" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="28" thickBot="1">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="H7" t="s">
-        <v>56</v>
+      <c r="D7" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F7" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="28" thickBot="1">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="1">
         <v>2</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="H8" t="s">
-        <v>57</v>
+      <c r="D8" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F8" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="28" thickBot="1">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="1">
         <v>2</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="H9" t="s">
-        <v>58</v>
+      <c r="D9" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F9" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="28" thickBot="1">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="1">
         <v>2</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="H10" t="s">
-        <v>59</v>
+      <c r="D10" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F10" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="28" thickBot="1">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="1">
         <v>2</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="H11" t="s">
-        <v>60</v>
+      <c r="D11" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F11" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="28" thickBot="1">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="1">
         <v>3</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="H12" t="s">
-        <v>61</v>
+      <c r="D12" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F12" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="28" thickBot="1">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="1">
         <v>3</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>108</v>
+      <c r="D13" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F13" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="28" thickBot="1">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="1">
         <v>3</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>88</v>
+      <c r="D14" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F14" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="28" thickBot="1">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C15" s="1">
         <v>3</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>88</v>
+      <c r="D15" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F15" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="28" thickBot="1">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="1">
         <v>3</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="28" thickBot="1">
-      <c r="A17" s="4" t="s">
+      <c r="D16" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F16" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="28" thickBot="1">
+      <c r="A17" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C17" s="1">
         <v>4</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="28" thickBot="1">
-      <c r="A18" s="4" t="s">
+      <c r="D17" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F17" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="28" thickBot="1">
+      <c r="A18" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C18" s="1">
         <v>4</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="28" thickBot="1">
-      <c r="A19" s="4" t="s">
+      <c r="D18" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F18" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="28" thickBot="1">
+      <c r="A19" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C19" s="1">
         <v>4</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="28" thickBot="1">
-      <c r="A20" s="4" t="s">
+      <c r="D19" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F19" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="28" thickBot="1">
+      <c r="A20" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C20" s="1">
         <v>4</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="28" thickBot="1">
-      <c r="A21" s="4" t="s">
+      <c r="D20" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F20" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="28" thickBot="1">
+      <c r="A21" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C21" s="1">
         <v>4</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="28" thickBot="1">
-      <c r="A22" s="4" t="s">
+      <c r="D21" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="28" thickBot="1">
+      <c r="A22" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C22" s="1">
         <v>5</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="28" thickBot="1">
-      <c r="A23" s="4" t="s">
+      <c r="D22" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F22" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="28" thickBot="1">
+      <c r="A23" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C23" s="1">
         <v>5</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="28" thickBot="1">
-      <c r="A24" s="4" t="s">
+      <c r="D23" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F23" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="28" thickBot="1">
+      <c r="A24" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C24" s="1">
         <v>5</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="28" thickBot="1">
-      <c r="A25" s="4" t="s">
+      <c r="D24" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F24" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="28" thickBot="1">
+      <c r="A25" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C25" s="1">
         <v>5</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="28" thickBot="1">
-      <c r="A26" s="4" t="s">
+      <c r="D25" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F25" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="28" thickBot="1">
+      <c r="A26" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C26" s="1">
         <v>5</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="28" thickBot="1">
-      <c r="A27" s="4" t="s">
+      <c r="D26" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F26" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="28" thickBot="1">
+      <c r="A27" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="3" t="s">
         <v>27</v>
       </c>
       <c r="C27" s="1">
         <v>6</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="28" thickBot="1">
-      <c r="A28" s="4" t="s">
+      <c r="D27" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F27" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="28" thickBot="1">
+      <c r="A28" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C28" s="1">
         <v>6</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="28" thickBot="1">
-      <c r="A29" s="4" t="s">
+      <c r="D28" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F28" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="28" thickBot="1">
+      <c r="A29" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C29" s="1">
         <v>6</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="28" thickBot="1">
-      <c r="A30" s="4" t="s">
+      <c r="D29" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F29" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="28" thickBot="1">
+      <c r="A30" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C30" s="1">
         <v>6</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E30" s="6" t="s">
+      <c r="D30" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="E30" s="5" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" ht="28" thickBot="1">
-      <c r="A31" s="4" t="s">
+      <c r="F30" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="28" thickBot="1">
+      <c r="A31" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C31" s="1">
         <v>6</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>139</v>
+      <c r="D31" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="F31" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
